--- a/backtest_runs/20260410_193731/by_symbol/JSML/JSML.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/JSML/JSML.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-3615.840000000006</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>96384.15999999999</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>103967.38</v>
@@ -771,7 +771,7 @@
         <v>-3130.379999999996</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>100837</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>102577.96</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>102577.96</v>
@@ -1231,7 +1231,7 @@
         <v>-418.5</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>107198.2</v>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>112303.9</v>
@@ -1415,7 +1415,7 @@
         <v>-6746.21999999999</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>105557.68</v>
@@ -1645,7 +1645,7 @@
         <v>-12588.47999999999</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>129897.64</v>
